--- a/v4/SystemTestPlan_v4.xlsx
+++ b/v4/SystemTestPlan_v4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohammedamine.medrar\Documents\Guru99 Bankng project\v4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohammedamine.medrar\Documents\Guru99 Banking project\v4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345AAABD-B152-494D-A103-06DD6BF37955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E27113F-3651-4C72-AF0E-79BEF2095A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14820" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Form Responses 1" sheetId="1" r:id="rId1"/>
@@ -1641,7 +1641,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1699,13 +1699,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1723,7 +1720,7 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2246,12 +2243,12 @@
       <c r="H1" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="I1" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
     </row>
     <row r="2" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -2276,12 +2273,12 @@
         <v>30</v>
       </c>
       <c r="H2" s="15"/>
-      <c r="I2" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
+      <c r="I2" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
     </row>
     <row r="3" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
@@ -2304,12 +2301,12 @@
         <v>36</v>
       </c>
       <c r="H3" s="15"/>
-      <c r="I3" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
-      <c r="L3" s="19"/>
+      <c r="I3" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
@@ -2332,12 +2329,12 @@
         <v>42</v>
       </c>
       <c r="H4" s="15"/>
-      <c r="I4" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
+      <c r="I4" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
@@ -2362,14 +2359,14 @@
         <v>49</v>
       </c>
       <c r="H5" s="15"/>
-      <c r="I5" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J5" s="21" t="s">
+      <c r="I5" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="20" t="s">
         <v>386</v>
       </c>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
     </row>
     <row r="6" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
@@ -2392,14 +2389,14 @@
         <v>55</v>
       </c>
       <c r="H6" s="15"/>
-      <c r="I6" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J6" s="21" t="s">
+      <c r="I6" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="20" t="s">
         <v>385</v>
       </c>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
     </row>
     <row r="7" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
@@ -2426,12 +2423,12 @@
       <c r="H7" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="I7" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
     </row>
     <row r="8" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
@@ -2454,12 +2451,12 @@
         <v>68</v>
       </c>
       <c r="H8" s="15"/>
-      <c r="I8" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
+      <c r="I8" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
     </row>
     <row r="9" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
@@ -2482,12 +2479,12 @@
         <v>68</v>
       </c>
       <c r="H9" s="15"/>
-      <c r="I9" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
+      <c r="I9" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
     </row>
     <row r="10" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
@@ -2510,12 +2507,12 @@
         <v>68</v>
       </c>
       <c r="H10" s="15"/>
-      <c r="I10" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
+      <c r="I10" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
     </row>
     <row r="11" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
@@ -2538,12 +2535,12 @@
         <v>68</v>
       </c>
       <c r="H11" s="15"/>
-      <c r="I11" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
+      <c r="I11" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
     </row>
     <row r="12" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
@@ -2570,12 +2567,12 @@
       <c r="H12" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="I12" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
+      <c r="I12" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
     </row>
     <row r="13" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
@@ -2598,12 +2595,12 @@
         <v>68</v>
       </c>
       <c r="H13" s="15"/>
-      <c r="I13" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
+      <c r="I13" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
     </row>
     <row r="14" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
@@ -2626,12 +2623,12 @@
         <v>68</v>
       </c>
       <c r="H14" s="15"/>
-      <c r="I14" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
+      <c r="I14" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
     </row>
     <row r="15" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
@@ -2656,12 +2653,12 @@
       <c r="H15" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="I15" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J15" s="19"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
+      <c r="I15" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
     </row>
     <row r="16" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
@@ -2686,12 +2683,12 @@
       <c r="H16" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="I16" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
+      <c r="I16" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
     </row>
     <row r="17" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
@@ -2716,12 +2713,12 @@
         <v>116</v>
       </c>
       <c r="H17" s="15"/>
-      <c r="I17" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
+      <c r="I17" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
     </row>
     <row r="18" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
@@ -2744,12 +2741,12 @@
       <c r="H18" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="I18" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
+      <c r="I18" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
     </row>
     <row r="19" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
@@ -2772,12 +2769,12 @@
         <v>68</v>
       </c>
       <c r="H19" s="15"/>
-      <c r="I19" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J19" s="19"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
+      <c r="I19" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
     </row>
     <row r="20" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
@@ -2802,12 +2799,12 @@
       <c r="H20" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="I20" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
+      <c r="I20" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
     </row>
     <row r="21" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
@@ -2832,12 +2829,12 @@
       <c r="H21" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="I21" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
+      <c r="I21" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
     </row>
     <row r="22" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
@@ -2862,12 +2859,12 @@
       <c r="H22" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="I22" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="19"/>
+      <c r="I22" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
     </row>
     <row r="23" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
@@ -2892,12 +2889,12 @@
       <c r="H23" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="I23" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
+      <c r="I23" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
     </row>
     <row r="24" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
@@ -2920,12 +2917,12 @@
         <v>155</v>
       </c>
       <c r="H24" s="15"/>
-      <c r="I24" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
+      <c r="I24" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
     </row>
     <row r="25" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
@@ -2950,12 +2947,12 @@
         <v>162</v>
       </c>
       <c r="H25" s="15"/>
-      <c r="I25" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
+      <c r="I25" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
     </row>
     <row r="26" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
@@ -2978,12 +2975,12 @@
       <c r="H26" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="I26" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="L26" s="19"/>
+      <c r="I26" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
     </row>
     <row r="27" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
@@ -3008,12 +3005,12 @@
         <v>174</v>
       </c>
       <c r="H27" s="15"/>
-      <c r="I27" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
+      <c r="I27" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
     </row>
     <row r="28" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
@@ -3038,12 +3035,12 @@
       <c r="H28" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="I28" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
+      <c r="I28" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
     </row>
     <row r="29" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
@@ -3066,12 +3063,12 @@
         <v>186</v>
       </c>
       <c r="H29" s="15"/>
-      <c r="I29" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
-      <c r="L29" s="19"/>
+      <c r="I29" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
     </row>
     <row r="30" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
@@ -3094,12 +3091,12 @@
         <v>191</v>
       </c>
       <c r="H30" s="15"/>
-      <c r="I30" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J30" s="19"/>
-      <c r="K30" s="19"/>
-      <c r="L30" s="19"/>
+      <c r="I30" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
     </row>
     <row r="31" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
@@ -3124,12 +3121,12 @@
         <v>198</v>
       </c>
       <c r="H31" s="15"/>
-      <c r="I31" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J31" s="19"/>
-      <c r="K31" s="19"/>
-      <c r="L31" s="19"/>
+      <c r="I31" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
     </row>
     <row r="32" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
@@ -3154,12 +3151,12 @@
       <c r="H32" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="I32" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
+      <c r="I32" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
     </row>
     <row r="33" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
@@ -3180,12 +3177,12 @@
         <v>209</v>
       </c>
       <c r="H33" s="15"/>
-      <c r="I33" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J33" s="19"/>
-      <c r="K33" s="19"/>
-      <c r="L33" s="19"/>
+      <c r="I33" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
     </row>
     <row r="34" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
@@ -3210,12 +3207,12 @@
         <v>215</v>
       </c>
       <c r="H34" s="15"/>
-      <c r="I34" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J34" s="19"/>
-      <c r="K34" s="19"/>
-      <c r="L34" s="19"/>
+      <c r="I34" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
     </row>
     <row r="35" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
@@ -3238,12 +3235,12 @@
         <v>221</v>
       </c>
       <c r="H35" s="15"/>
-      <c r="I35" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J35" s="19"/>
-      <c r="K35" s="19"/>
-      <c r="L35" s="19"/>
+      <c r="I35" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
     </row>
     <row r="36" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
@@ -3266,12 +3263,12 @@
         <v>68</v>
       </c>
       <c r="H36" s="15"/>
-      <c r="I36" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J36" s="19"/>
-      <c r="K36" s="19"/>
-      <c r="L36" s="19"/>
+      <c r="I36" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
     </row>
     <row r="37" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="17"/>
@@ -3283,8 +3280,8 @@
       <c r="G37" s="17"/>
       <c r="H37" s="17"/>
       <c r="I37" s="17"/>
-      <c r="J37" s="19"/>
-      <c r="K37" s="19"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3367,7 +3364,7 @@
       <c r="H2" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="22" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3394,7 +3391,7 @@
       <c r="H3" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="I3" s="23" t="s">
+      <c r="I3" s="22" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3421,7 +3418,7 @@
       <c r="H4" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="23" t="s">
+      <c r="I4" s="22" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3450,7 +3447,7 @@
       <c r="H5" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="I5" s="23" t="s">
+      <c r="I5" s="22" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3479,7 +3476,7 @@
       <c r="H6" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="I6" s="23" t="s">
+      <c r="I6" s="22" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3508,7 +3505,7 @@
       <c r="H7" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="I7" s="23" t="s">
+      <c r="I7" s="22" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3533,7 +3530,7 @@
       <c r="H8" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="I8" s="24" t="s">
+      <c r="I8" s="23" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3560,7 +3557,7 @@
       <c r="H9" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="I9" s="23" t="s">
+      <c r="I9" s="22" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3587,7 +3584,7 @@
       <c r="H10" s="15" t="s">
         <v>270</v>
       </c>
-      <c r="I10" s="23" t="s">
+      <c r="I10" s="22" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3614,7 +3611,7 @@
       <c r="H11" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="I11" s="23" t="s">
+      <c r="I11" s="22" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3641,7 +3638,7 @@
       <c r="H12" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="I12" s="23" t="s">
+      <c r="I12" s="22" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3670,7 +3667,7 @@
       <c r="H13" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="I13" s="23" t="s">
+      <c r="I13" s="22" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3697,7 +3694,7 @@
       <c r="H14" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="I14" s="23" t="s">
+      <c r="I14" s="22" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3726,7 +3723,7 @@
       <c r="H15" s="15" t="s">
         <v>296</v>
       </c>
-      <c r="I15" s="23" t="s">
+      <c r="I15" s="22" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3753,7 +3750,7 @@
       <c r="H16" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="I16" s="22" t="s">
+      <c r="I16" s="21" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3780,7 +3777,7 @@
       <c r="H17" s="15" t="s">
         <v>305</v>
       </c>
-      <c r="I17" s="25" t="s">
+      <c r="I17" s="24" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4083,7 +4080,7 @@
       <c r="G2" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="22" t="s">
         <v>31</v>
       </c>
       <c r="I2" s="5"/>
@@ -4108,7 +4105,7 @@
       <c r="G3" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="H3" s="23" t="s">
+      <c r="H3" s="22" t="s">
         <v>31</v>
       </c>
       <c r="I3" s="5"/>
@@ -4133,7 +4130,7 @@
       <c r="G4" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="H4" s="23" t="s">
+      <c r="H4" s="22" t="s">
         <v>31</v>
       </c>
       <c r="I4" s="5"/>
@@ -4158,7 +4155,7 @@
       <c r="G5" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="H5" s="23" t="s">
+      <c r="H5" s="22" t="s">
         <v>31</v>
       </c>
       <c r="I5" s="5"/>
@@ -4185,10 +4182,10 @@
       <c r="G6" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="H6" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="27"/>
+      <c r="H6" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="26"/>
     </row>
     <row r="7" spans="1:9" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
@@ -4210,7 +4207,7 @@
       <c r="G7" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="H7" s="26" t="s">
+      <c r="H7" s="25" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="5"/>
@@ -4229,7 +4226,7 @@
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="15"/>
-      <c r="H8" s="26" t="s">
+      <c r="H8" s="25" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="5"/>
@@ -4256,7 +4253,7 @@
       <c r="G9" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="H9" s="23" t="s">
+      <c r="H9" s="22" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="5"/>
@@ -4283,7 +4280,7 @@
       <c r="G10" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="H10" s="23" t="s">
+      <c r="H10" s="22" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="5"/>
@@ -4310,7 +4307,7 @@
       <c r="G11" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="H11" s="23" t="s">
+      <c r="H11" s="22" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="5"/>
@@ -4337,7 +4334,7 @@
       <c r="G12" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="H12" s="23" t="s">
+      <c r="H12" s="22" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="5"/>
@@ -4362,7 +4359,7 @@
       <c r="G13" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="H13" s="23" t="s">
+      <c r="H13" s="22" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="5"/>
@@ -4389,7 +4386,7 @@
       <c r="G14" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="H14" s="23" t="s">
+      <c r="H14" s="22" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="5"/>
@@ -4414,7 +4411,7 @@
       <c r="G15" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="H15" s="23" t="s">
+      <c r="H15" s="22" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="5"/>
@@ -4441,7 +4438,7 @@
       <c r="G16" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="H16" s="23" t="s">
+      <c r="H16" s="22" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="5"/>
@@ -4466,7 +4463,7 @@
       <c r="G17" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="H17" s="23" t="s">
+      <c r="H17" s="22" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="5"/>
@@ -4491,7 +4488,7 @@
       <c r="G18" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="H18" s="23" t="s">
+      <c r="H18" s="22" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="5"/>
@@ -4518,7 +4515,7 @@
       <c r="G19" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="H19" s="23" t="s">
+      <c r="H19" s="22" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="5"/>
